--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2423" uniqueCount="2421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2457" uniqueCount="2455">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251017120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-17T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1782,13 +1782,13 @@
     <t>0523</t>
   </si>
   <si>
-    <t>Sevrage simple</t>
+    <t>Sevrage à faible risque de complication médicale (sevrage simple)</t>
   </si>
   <si>
     <t>0524</t>
   </si>
   <si>
-    <t>Sevrage complexe</t>
+    <t>Sevrage à fort risque de complication médicale (sevrage complexe)</t>
   </si>
   <si>
     <t>0525</t>
@@ -3402,13 +3402,13 @@
     <t>0849</t>
   </si>
   <si>
-    <t>Suivi cardiologique avec organisation de la prise en charge</t>
+    <t>Coordination pour assurer le suivi cardiologique avec organisation de la prise en charge</t>
   </si>
   <si>
     <t>0850</t>
   </si>
   <si>
-    <t>Suivi gynécologique avec organisation de la prise en charge</t>
+    <t>Coordination pour assurer le suivi gynécologique avec organisation de la prise en charge</t>
   </si>
   <si>
     <t>0851</t>
@@ -3474,7 +3474,7 @@
     <t>0861</t>
   </si>
   <si>
-    <t>Dépistage et suivi des pathologies endocriniennes</t>
+    <t>Dépistage et suivi biologique des pathologies endocriniennes</t>
   </si>
   <si>
     <t>0862</t>
@@ -3609,12 +3609,6 @@
     <t>Soins permanents continus par délégation / Présence aide-soignant de nuit</t>
   </si>
   <si>
-    <t>0887</t>
-  </si>
-  <si>
-    <t>Chirurgie sénologique</t>
-  </si>
-  <si>
     <t>0888</t>
   </si>
   <si>
@@ -3858,13 +3852,13 @@
     <t>0965</t>
   </si>
   <si>
-    <t>Réadaptation du cancer du sein</t>
+    <t>Rééducation du cancer du sein</t>
   </si>
   <si>
     <t>0966</t>
   </si>
   <si>
-    <t>Réadaptation des cicatrices</t>
+    <t>Rééducation des cicatrices</t>
   </si>
   <si>
     <t>0967</t>
@@ -3876,7 +3870,7 @@
     <t>0968</t>
   </si>
   <si>
-    <t>Réadaptation de la main</t>
+    <t>Rééducation de la main</t>
   </si>
   <si>
     <t>0969</t>
@@ -3900,7 +3894,7 @@
     <t>0972</t>
   </si>
   <si>
-    <t>Réadaptation maxillo-faciale</t>
+    <t>Rééducation maxillo-faciale</t>
   </si>
   <si>
     <t>0973</t>
@@ -4146,7 +4140,7 @@
     <t>1013</t>
   </si>
   <si>
-    <t>Vaccination contre les infections sexuellement transmissible (IST)</t>
+    <t>Vaccination contre les infections sexuellement transmissibles (IST)</t>
   </si>
   <si>
     <t>1014</t>
@@ -4860,7 +4854,7 @@
     <t>1135</t>
   </si>
   <si>
-    <t>Angio IRM cérébral</t>
+    <t>Angio IRM cérébrale</t>
   </si>
   <si>
     <t>1136</t>
@@ -5184,7 +5178,7 @@
     <t>1191</t>
   </si>
   <si>
-    <t>Embolisation cérébrale anévrisme MAV</t>
+    <t>Embolisation cérébrale anévrisme Malformation Antéro Veineuse (MAV)</t>
   </si>
   <si>
     <t>1192</t>
@@ -5352,7 +5346,7 @@
     <t>1220</t>
   </si>
   <si>
-    <t>IRM CAI et APC</t>
+    <t>IRM Conduit Auditif Interne (CAI) et Angle Ponto-Cérébelleux (APC)</t>
   </si>
   <si>
     <t>1221</t>
@@ -5604,7 +5598,7 @@
     <t>1262</t>
   </si>
   <si>
-    <t>Scanner pré TAVI</t>
+    <t>Scanner pré Implantation d'une valve aortique par voie percutanée (TAVI)</t>
   </si>
   <si>
     <t>1263</t>
@@ -6666,7 +6660,7 @@
     <t>1454</t>
   </si>
   <si>
-    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL)</t>
+    <t>Evaluation et suivi standardisé clinique et paraclinique des commotions cérébrales (Traumatisme Crânien Léger - TCL) dans un cadre sportif</t>
   </si>
   <si>
     <t>1455</t>
@@ -6738,7 +6732,7 @@
     <t>1467</t>
   </si>
   <si>
-    <t>Examen visuel du sportif</t>
+    <t>Evaluation de la vue du sportif </t>
   </si>
   <si>
     <t>1468</t>
@@ -6798,19 +6792,19 @@
     <t>1478</t>
   </si>
   <si>
-    <t>Réadaptation des migraines et céphalées</t>
+    <t>Rééducation des migraines et céphalées</t>
   </si>
   <si>
     <t>1479</t>
   </si>
   <si>
-    <t>Réadaptation abdominale du post partum</t>
+    <t>Rééducation abdominale du post partum</t>
   </si>
   <si>
     <t>1480</t>
   </si>
   <si>
-    <t>Réadaptation abdominale préopératoire et post opératoire</t>
+    <t>Rééducation abdominale préopératoire et post opératoire</t>
   </si>
   <si>
     <t>1481</t>
@@ -7267,6 +7261,114 @@
   </si>
   <si>
     <t>Rééducation des paralysies cérébrales et polyhandicaps</t>
+  </si>
+  <si>
+    <t>1557</t>
+  </si>
+  <si>
+    <t>Prise en charge de bébé grand prématuré (&lt; 28 SA)</t>
+  </si>
+  <si>
+    <t>1558</t>
+  </si>
+  <si>
+    <t>Veille sanitaire et analyse de produit in situ</t>
+  </si>
+  <si>
+    <t>1559</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées au cannabis et cannabinoïdes</t>
+  </si>
+  <si>
+    <t>1560</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux psychostimulants (cocaïne, crack, dérivés des amphétamines, ecstasy, MDMA, cathinones de synthèse…)</t>
+  </si>
+  <si>
+    <t>1561</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux opiacés (héroïne, morphinique)</t>
+  </si>
+  <si>
+    <t>1562</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux autres substances (hallucinogènes, champignons, LSD, kétamine)</t>
+  </si>
+  <si>
+    <t>1563</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées aux benzodiazépines et autres sédatifs</t>
+  </si>
+  <si>
+    <t>1564</t>
+  </si>
+  <si>
+    <t>Evaluation et suivi des addictions liées au chemsex (cathinones de synthèse, poppers, etc)</t>
+  </si>
+  <si>
+    <t>1570</t>
+  </si>
+  <si>
+    <t>Rééducation vésico-sphinctérienne</t>
+  </si>
+  <si>
+    <t>1571</t>
+  </si>
+  <si>
+    <t>Rééducation anorectale</t>
+  </si>
+  <si>
+    <t>1572</t>
+  </si>
+  <si>
+    <t>Rééducation des troubles de la déglutition</t>
+  </si>
+  <si>
+    <t>1573</t>
+  </si>
+  <si>
+    <t>Rééducation post-COVID (COVID long)</t>
+  </si>
+  <si>
+    <t>1574</t>
+  </si>
+  <si>
+    <t>Centre Ressources Autisme (CRA)</t>
+  </si>
+  <si>
+    <t>1575</t>
+  </si>
+  <si>
+    <t>Centre de référence des Troubles du Langage et de l’Apprentissage (CRTLA)</t>
+  </si>
+  <si>
+    <t>1576</t>
+  </si>
+  <si>
+    <t>Centre de référence du Trouble Déficit de l’Attention avec ou sans Hyperactivité (CRTDAH)</t>
+  </si>
+  <si>
+    <t>1577</t>
+  </si>
+  <si>
+    <t>Centre de compétence centre mémoire ressources et recherche (CMRR)</t>
+  </si>
+  <si>
+    <t>1578</t>
+  </si>
+  <si>
+    <t>Centre expert Parkinson</t>
+  </si>
+  <si>
+    <t>1579</t>
+  </si>
+  <si>
+    <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
   </si>
   <si>
     <t/>
@@ -7537,7 +7639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1198"/>
+  <dimension ref="A1:B1215"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -17117,15 +17219,151 @@
         <v>2418</v>
       </c>
       <c r="B1197" t="s" s="2">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="1198">
       <c r="A1198" t="s" s="2">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="B1198" t="s" s="2">
-        <v>2420</v>
+        <v>2421</v>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="s" s="2">
+        <v>2422</v>
+      </c>
+      <c r="B1199" t="s" s="2">
+        <v>2423</v>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="s" s="2">
+        <v>2424</v>
+      </c>
+      <c r="B1200" t="s" s="2">
+        <v>2425</v>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="s" s="2">
+        <v>2426</v>
+      </c>
+      <c r="B1201" t="s" s="2">
+        <v>2427</v>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="s" s="2">
+        <v>2428</v>
+      </c>
+      <c r="B1202" t="s" s="2">
+        <v>2429</v>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="s" s="2">
+        <v>2430</v>
+      </c>
+      <c r="B1203" t="s" s="2">
+        <v>2431</v>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="s" s="2">
+        <v>2432</v>
+      </c>
+      <c r="B1204" t="s" s="2">
+        <v>2433</v>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="s" s="2">
+        <v>2434</v>
+      </c>
+      <c r="B1205" t="s" s="2">
+        <v>2435</v>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="s" s="2">
+        <v>2436</v>
+      </c>
+      <c r="B1206" t="s" s="2">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="s" s="2">
+        <v>2438</v>
+      </c>
+      <c r="B1207" t="s" s="2">
+        <v>2439</v>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="s" s="2">
+        <v>2440</v>
+      </c>
+      <c r="B1208" t="s" s="2">
+        <v>2441</v>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="s" s="2">
+        <v>2442</v>
+      </c>
+      <c r="B1209" t="s" s="2">
+        <v>2443</v>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="s" s="2">
+        <v>2444</v>
+      </c>
+      <c r="B1210" t="s" s="2">
+        <v>2445</v>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="s" s="2">
+        <v>2446</v>
+      </c>
+      <c r="B1211" t="s" s="2">
+        <v>2447</v>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="s" s="2">
+        <v>2448</v>
+      </c>
+      <c r="B1212" t="s" s="2">
+        <v>2449</v>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="s" s="2">
+        <v>2450</v>
+      </c>
+      <c r="B1213" t="s" s="2">
+        <v>2451</v>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="s" s="2">
+        <v>2452</v>
+      </c>
+      <c r="B1214" t="s" s="2">
+        <v>2452</v>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="s" s="2">
+        <v>2453</v>
+      </c>
+      <c r="B1215" t="s" s="2">
+        <v>2454</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -3906,7 +3906,7 @@
     <t>0974</t>
   </si>
   <si>
-    <t>Réadaptation de la Mucoviscidose</t>
+    <t>Rééducation de la Mucoviscidose</t>
   </si>
   <si>
     <t>0975</t>
